--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Collegetown_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Collegetown_20251031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,6 +983,60 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TN374</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Natalie's - Lemonade</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9.30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>9.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TN380</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Natalie's - Strawberry Lemonade</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
